--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,31 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-28 17:24</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
         </is>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,31 @@
         </is>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-29 11:30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
         </is>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,31 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-30 11:59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
         </is>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,31 @@
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:50</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
         </is>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,31 @@
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-01 11:36</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
         </is>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,31 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:35</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,6 +619,31 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bolígrafos Bic Cristal Dura+ Mediano Negro Cj12 - Marchand</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,1385 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:55</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:55</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:04</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:05</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>169.09</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:06</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:10</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:11</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:11</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:12</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:12</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:14</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:14</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,1385 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:22</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:23</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:23</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:23</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:23</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:24</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:24</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:24</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:28</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:28</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:28</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:29</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:29</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:30</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>307.71</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:30</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:30</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:30</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:31</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:31</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:32</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:32</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>73.06</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:32</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:33</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:33</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:33</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:33</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:34</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:34</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:34</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>169.09</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:36</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:36</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:36</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:37</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:37</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:38</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:40</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:42</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:42</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:42</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:42</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:43</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:43</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:43</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:44</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:44</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:44</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:45</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3202,6 +3202,1385 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:32</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:32</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:32</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:33</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:33</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:33</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:33</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:34</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:34</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:37</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:37</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:37</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:38</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:38</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:38</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:39</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>307.71</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:39</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:39</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:40</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:40</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:40</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:41</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:41</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:41</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>73.06</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:42</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:42</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:42</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:42</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:43</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:43</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:43</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:43</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:44</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:44</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>169.09</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:44</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:45</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:45</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:45</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:45</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:46</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:46</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:49</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:49</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:50</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:50</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:50</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:50</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:51</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:51</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:51</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:52</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:52</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:52</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:52</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:53</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4581,6 +4581,1383 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:42</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:42</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:43</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:43</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:43</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:43</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:44</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:44</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:44</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:47</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:47</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:48</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:48</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:48</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:49</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:49</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>307.71</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:49</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:50</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:50</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:50</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:51</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:51</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:51</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:51</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>73.06</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:52</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:52</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:52</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:52</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:53</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:53</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>200.1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:53</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:54</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:54</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:54</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>169.09</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:54</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:55</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:55</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:55</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:56</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:56</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:56</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:57</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:57</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:57</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:57</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:58</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:58</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:58</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:59</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:59</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:59</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-06 10:59</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,6 +1819,1381 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:35</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:36</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:36</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:37</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:37</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:37</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:38</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:38</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:38</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:38</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:39</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:39</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:39</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:40</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:40</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:40</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:41</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:41</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:41</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:41</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:42</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:42</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:42</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>73.06</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:43</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:43</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:43</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:44</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:44</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:44</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:44</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:45</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:45</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:45</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:46</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:46</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:46</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:47</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:47</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:47</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:47</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:48</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:48</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:48</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:49</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:49</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:49</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:49</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:50</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>214.98</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:50</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:51</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:51</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:51</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:51</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:52</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3194,6 +3194,1381 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:45</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:46</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:46</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:46</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:46</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:47</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:47</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:47</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:48</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:48</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:48</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:49</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:49</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:49</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:50</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:50</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:50</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:50</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:51</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:51</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:51</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:52</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:52</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:52</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:53</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:53</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:53</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:54</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:54</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:54</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:54</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:55</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:55</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:55</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:56</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:56</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:56</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:56</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:57</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:57</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:57</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:58</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:58</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:58</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:59</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:59</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:59</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:59</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>214.98</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:00</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:01</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:02</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,6 +1819,1381 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:29</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:29</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:30</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:31</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:31</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:31</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:32</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:32</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:32</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:33</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:33</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:33</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:34</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:34</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:34</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:35</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:35</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:35</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:36</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:36</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:36</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:36</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:40</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:40</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:40</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:41</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:41</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:41</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:42</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:42</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:42</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:42</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:43</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:43</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:43</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:44</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>214.98</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:44</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:44</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1821,6 +1821,1383 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:31</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:31</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:31</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:32</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:32</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:32</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:32</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:35</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:36</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:36</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:36</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:37</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:37</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:37</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:37</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:38</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:38</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:38</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:39</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:39</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:39</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:40</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:40</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:40</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:44</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:44</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:44</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:45</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:45</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:45</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:45</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:46</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:46</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:46</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:47</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:47</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:47</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>214.98</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:48</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:48</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3198,6 +3198,1381 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:44</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/5/Bol%C3%ADgrafos%20Bic%20Fino%20Color%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:45</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/10049/Bol%C3%ADgrafos%20Paper%20Mate%20Kilom%C3%A9trico%20Fino%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:45</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12849/Bol%C3%ADgrafo%20Azor%20Pin%20Point%20Punto%20Fino%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:45</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1/Bol%C3%ADgrafos%20Bic%20Cristal%20Dura%2B%20Mediano%20Color%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:46</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/61/Bol%C3%ADgrafos%20Paper%20Mate%20Ink%20Joy%20Km%20Punto%20Medio%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:46</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12844/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:46</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/12848/Bol%C3%ADgrafos%20Azor%20Pin%20Point%20Punto%20Mediano%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:47</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1250/Cartulina%20Scribe%20Expression%20Blanco%20135gr%2050%20x%2065%20cm%20100H</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:47</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3902/Cinta%20Corte%20F%C3%A1cil%20Janel%20119%20Transparente%2018mmx33M%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:47</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/254/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:47</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/255/Colores%20Dixon%20Blanca%20Nieves%20Corto%20Largo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:48</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/251/Colores%20Dixon%20Mapita%20Corto%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:48</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/252/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:48</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/253/Colores%20Dixon%20Mapita%20Largo%20Redondo%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:48</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/4908/Colores%20Norma%20Redondos%20Largos%20Surtidos%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:49</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/309/Coloress%20Norma%20Redondos%20Largos%20CJ36</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:49</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/307/Colores%20Norma%20Redondos%20Largos%20CJ24%2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:49</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/304/Colores%20Norma%20Redondos%20Largos%20CJ13%2B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:50</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>201.51</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/612/Colores%20Prismacolor%20%20surtidos%20redondos%20largos%20CJ24</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:50</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/303/Colores%20Vinci%20Vividel%20Largos%20Redondos%20Caja%20con%2012%20piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:50</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/17158/Colores%20Vividel%20Triangular%20Largo%20Surtido%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:50</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1639/Papel%20Crep%C3%A9%20Colibr%C3%AD%20Blanco%20con%2010%20Hojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:51</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2216/Cray%C3%B3n%20Vinci%20Vividel%20Grueso%20Redondo%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:51</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1576/Cuaderno%20profesional%20Norma%20360%20cosido%20cuadro%20grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:51</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/950/Cuaderno%20Scribe%20Profesional%20Escolar%20Plus%20Espiral%20Sencilla%20Raya%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:52</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1046/Cuaderno%20Scribe%20Profesional%20Mega%20Plus%20Espiral%20Sencilla%20Cuadro%20Grande%20100h</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:52</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/search/2926</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:52</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/24038/Goma%20Factis%20S20%20Color%20Blanco%20Migaj%C3%B3n%20Caja%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:53</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1815/Goma%20para%20Borrar%20Pelikan%20Tipo%20Migaj%C3%B3n%20M20%20CJ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:53</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/289/L%C3%A1piz%20Grafito%20Dixon%20M%C3%A9trico%20CJ100</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:53</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/334/L%C3%A1piz%20Grafito%20Maped%20Triangular%20Madera%20%232%20HB%20Bote%20con%2072%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:53</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/827/Marcador%20Permanente%20Sharpie%20Doble%20Punta%20Negro%20Caja%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/818/Marcador%20Permanente%20Sharpie%20Esterbrook%20%20Negro%20CJ12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>152.19</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3771/Mica%20Adherible%20TRANSFER%20Paquete%20con%2010%20pliegos%2066%20x%2050%20cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1231/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1237/Papel%20Scribe%20Duplicador%20Blanco%2078%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/902/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/921/Papel%20Facia%20Bond%20Copamex%20Blanco%20Doble%20Carta%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/927/Papel%20Facia%20Bond%20Copamex%20Blanco%20Tama%C3%B1o%20Oficio%2075gr%20P500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:56</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1233/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:56</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1240/Papel%20Scribe%20Fotobond%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:56</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/26375/Papel%20Bond%20DIEM%20Premium%2075gr%20Tama%C3%B1o%20Carta%20Blancura%2099%20con%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:57</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1230/Papel%20Scribe%20Ecol%C3%B3gico%20Blanco%2075gr%20Tama%C3%B1o%20Carta%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:57</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/1236/Papel%20Scribe%20Ecologico%20Blanco%2075%20gr%20Tama%C3%B1o%20Oficio%20500H</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:57</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/7064/Pegamento%20Instantaneo%20Kola%20Loka%20Goterito%203.5gr%20BL1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:58</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2030/Pegamento%20L%C3%A1piz%20Adhesivo%20Escolar%20Bully%2011gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:58</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2410/L%C3%A1piz%20Adhesivo%20Dixon%2021gr%20Charola%20con%2020%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:58</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2411/L%C3%A1piz%20Adhesivo%20Dixon%2036gr%20Charola%20con%2012%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:58</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>214.98</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2094/L%C3%A1piz%20Adhesivo%20Dixon%208gr%20Charola%20con%2030%20Piezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:59</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>239.89</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2020/Pegamento%20L%C3%A1piz%20Adhesivo%20Pritt%2042GR%20CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:59</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2257</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2257/Pintura%20Politec%20Acr%C3%ADlico%20Color%20Amarillo%20Claro%2020ml%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:59</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3019/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20100ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:00</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/2940/Pintura%20Politec%20Acr%C3%ADlica%20%20Color%20Blanco%20Titanio%20250ml%20Pz</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:00</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/3823/Registrador%20Lefort%20Tama%C3%B1o%20Carta%20Color%20Marmoleado%201%20Pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:00</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.marchand.com.mx/product/18107/Tijera%20Amigos%20Punta%20Roma%20Troquelada%205.0%20B1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
